--- a/docs/rag_project_log_rev1.xlsx
+++ b/docs/rag_project_log_rev1.xlsx
@@ -19,8 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_다음할일" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_진행이력'!$A$4:$G$79</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_산출물목록'!$A$4:$G$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_진행이력'!$A$4:$G$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_산출물목록'!$A$4:$G$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3_파이프라인점검'!$A$4:$J$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4_골든셋현황'!$A$4:$J$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5_실험이력'!$A$4:$O$204</definedName>
@@ -705,7 +705,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>rag_checklist_rev9.xlsx `소스별_컬럼정의`</t>
+          <t>rag_checklist_rev10.xlsx `소스별_컬럼정의`</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>rag_checklist_rev9.xlsx</t>
+          <t>rag_checklist_rev10.xlsx</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2802,12 +2802,36 @@
       <c r="G39" s="12" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="n"/>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>#36</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>보완</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>기존 엑셀에 신규 도구 반영 · 수식 캐시 중복 주입 버그(파일 손상) 수정</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>golden_eval_pack_rev4(1b · 프리셋) · rag_checklist_rev10(단계별_실행도구) · golden_set_example_rev2</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
       <c r="G40" s="12" t="n"/>
     </row>
     <row r="41">
@@ -3161,57 +3185,66 @@
       <c r="F79" s="6" t="n"/>
       <c r="G79" s="12" t="n"/>
     </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="n"/>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="6" t="n"/>
+      <c r="G80" s="12" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>집계</t>
         </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="13" t="inlineStr">
-        <is>
-          <t>총 이력</t>
-        </is>
-      </c>
-      <c r="B82" s="14">
-        <f>COUNTIF(B5:B79,"&lt;&gt;")</f>
-        <v>35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>총 이력</t>
         </is>
       </c>
       <c r="B83" s="14">
-        <f>COUNTIF(F5:F79,"완료")</f>
-        <v>35</v>
+        <f>COUNTIF(B5:B80,"&lt;&gt;")</f>
+        <v>36</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="B84" s="14">
+        <f>COUNTIF(F5:F80,"완료")</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
           <t>진행 · 보류</t>
         </is>
       </c>
-      <c r="B84" s="14">
-        <f>COUNTIF(F5:F79,"진행")+COUNTIF(F5:F79,"보류")</f>
+      <c r="B85" s="14">
+        <f>COUNTIF(F5:F80,"진행")+COUNTIF(F5:F80,"보류")</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G79"/>
+  <autoFilter ref="A4:G80"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:F79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"완료,진행,보류"</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"진단,설계,문서,코드,평가,환경,배포,보완,확장,범위,확인,판단,산출"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3226,7 +3259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4108,12 +4141,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>rag_checklist_rev9.xlsx</t>
+          <t>rag_checklist_rev10.xlsx</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>체크리스트 · 컬럼 정의 기입본</t>
+          <t>체크리스트 · 컬럼 정의 · 단계별 실행 도구(S번호↔노트북)</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -4121,7 +4154,11 @@
           <t>rag_lab/docs/</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>신규 시트</t>
+        </is>
+      </c>
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="12" t="n"/>
     </row>
@@ -4133,12 +4170,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>golden_eval_pack_rev3.xlsx</t>
+          <t>golden_eval_pack_rev4.xlsx</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>골든셋 · 평가 기입본</t>
+          <t>골든셋 · 평가 기입본 (LLM 골든셋 검수 · 프리셋 열 포함)</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -4146,7 +4183,11 @@
           <t>rag_lab/docs/</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr"/>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>신규 시트 1b</t>
+        </is>
+      </c>
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="12" t="n"/>
     </row>
@@ -4158,12 +4199,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>metric_catalog_template_rev1.xlsx</t>
+          <t>golden_set_example_rev2.xlsx</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>정형 지표 정의서 양식</t>
+          <t>골든셋 실물 예시 — LLM 생성 · 근거 연결 포함 9종</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -4171,36 +4212,36 @@
           <t>rag_lab/docs/</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr"/>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
       <c r="F38" s="12" t="n"/>
       <c r="G38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>엑셀</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>golden/answer_golden_v1.csv</t>
+          <t>metric_catalog_template_rev1.xlsx</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>사외 정보 기반 질문 60건</t>
+          <t>정형 지표 정의서 양식</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>rag_lab/golden/</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>근거 연결 필요</t>
-        </is>
-      </c>
+          <t>rag_lab/docs/</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr"/>
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="12" t="n"/>
     </row>
@@ -4212,12 +4253,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>golden/smoke20.csv</t>
+          <t>golden/answer_golden_v1.csv</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>스모크 20문항</t>
+          <t>사외 정보 기반 질문 60건</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -4225,16 +4266,36 @@
           <t>rag_lab/golden/</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>근거 연결 필요</t>
+        </is>
+      </c>
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="12" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="n"/>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>데이터</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>golden/smoke20.csv</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>스모크 20문항</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>rag_lab/golden/</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr"/>
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="12" t="n"/>
     </row>
@@ -4409,14 +4470,23 @@
       <c r="F60" s="12" t="n"/>
       <c r="G60" s="12" t="n"/>
     </row>
+    <row r="61">
+      <c r="A61" s="6" t="n"/>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="12" t="n"/>
+      <c r="G61" s="12" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G60"/>
+  <autoFilter ref="A4:G61"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"적용,검토중,미적용,해당없음"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/rag_project_log_rev1.xlsx
+++ b/docs/rag_project_log_rev1.xlsx
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_진행이력'!$A$4:$G$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_산출물목록'!$A$4:$G$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_산출물목록'!$A$4:$G$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3_파이프라인점검'!$A$4:$J$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4_골든셋현황'!$A$4:$J$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5_실험이력'!$A$4:$O$204</definedName>
@@ -3259,7 +3259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3983,12 +3983,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>rag_runbook_rev1.html</t>
+          <t>rag_runbook_t2_rev1.html</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>전체 실행 안내서 — 먼저 읽는 문서</t>
+          <t>T2 보고서판 안내서 — 도식 13장 · 개념 설명용</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>rag_checklist_sheet_rev9.html</t>
+          <t>rag_runbook_rev1.html</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>단계별 체크리스트 · 소스별 컬럼 정의</t>
+          <t>실행 안내서(원본) — 절차 · FAQ 중심</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>rag_design_guide_rev4.html</t>
+          <t>rag_checklist_sheet_rev9.html</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>설계 원본</t>
+          <t>단계별 체크리스트 · 소스별 컬럼 정의</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -4062,12 +4062,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>rag_quest_board_rev4.html</t>
+          <t>rag_design_guide_rev4.html</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>옵션 사전</t>
+          <t>설계 원본</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>query_flow_example_rev2.html</t>
+          <t>rag_quest_board_rev4.html</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>혼합 질의 흐름 · 지표 정의서 예시</t>
+          <t>옵션 사전</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -4107,17 +4107,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>엑셀</t>
+          <t>문서</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>rag_project_log_rev1.xlsx</t>
+          <t>query_flow_example_rev2.html</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>이력 대장 — 본 파일</t>
+          <t>혼합 질의 흐름 · 지표 정의서 예시</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -4125,11 +4125,7 @@
           <t>rag_lab/docs/</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
+      <c r="E35" s="6" t="inlineStr"/>
       <c r="F35" s="12" t="n"/>
       <c r="G35" s="12" t="n"/>
     </row>
@@ -4141,12 +4137,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>rag_checklist_rev10.xlsx</t>
+          <t>rag_project_log_rev1.xlsx</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>체크리스트 · 컬럼 정의 · 단계별 실행 도구(S번호↔노트북)</t>
+          <t>이력 대장 — 본 파일</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -4156,7 +4152,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>신규 시트</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="F36" s="12" t="n"/>
@@ -4170,12 +4166,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>golden_eval_pack_rev4.xlsx</t>
+          <t>rag_checklist_rev10.xlsx</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>골든셋 · 평가 기입본 (LLM 골든셋 검수 · 프리셋 열 포함)</t>
+          <t>체크리스트 · 컬럼 정의 · 단계별 실행 도구(S번호↔노트북)</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -4185,7 +4181,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>신규 시트 1b</t>
+          <t>신규 시트</t>
         </is>
       </c>
       <c r="F37" s="12" t="n"/>
@@ -4199,12 +4195,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>golden_set_example_rev2.xlsx</t>
+          <t>golden_eval_pack_rev4.xlsx</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>골든셋 실물 예시 — LLM 생성 · 근거 연결 포함 9종</t>
+          <t>골든셋 · 평가 기입본 (LLM 골든셋 검수 · 프리셋 열 포함)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -4214,7 +4210,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>신규 시트 1b</t>
         </is>
       </c>
       <c r="F38" s="12" t="n"/>
@@ -4228,12 +4224,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>metric_catalog_template_rev1.xlsx</t>
+          <t>golden_set_example_rev2.xlsx</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>정형 지표 정의서 양식</t>
+          <t>골든셋 실물 예시 — LLM 생성 · 근거 연결 포함 9종</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -4241,36 +4237,36 @@
           <t>rag_lab/docs/</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>엑셀</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>golden/answer_golden_v1.csv</t>
+          <t>metric_catalog_template_rev1.xlsx</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>사외 정보 기반 질문 60건</t>
+          <t>정형 지표 정의서 양식</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>rag_lab/golden/</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>근거 연결 필요</t>
-        </is>
-      </c>
+          <t>rag_lab/docs/</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr"/>
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="12" t="n"/>
     </row>
@@ -4282,12 +4278,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>golden/smoke20.csv</t>
+          <t>golden/answer_golden_v1.csv</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>스모크 20문항</t>
+          <t>사외 정보 기반 질문 60건</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -4295,16 +4291,36 @@
           <t>rag_lab/golden/</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>근거 연결 필요</t>
+        </is>
+      </c>
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="12" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="n"/>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>데이터</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>golden/smoke20.csv</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>스모크 20문항</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>rag_lab/golden/</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr"/>
       <c r="F42" s="12" t="n"/>
       <c r="G42" s="12" t="n"/>
     </row>
@@ -4479,14 +4495,23 @@
       <c r="F61" s="12" t="n"/>
       <c r="G61" s="12" t="n"/>
     </row>
+    <row r="62">
+      <c r="A62" s="6" t="n"/>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="12" t="n"/>
+      <c r="G62" s="12" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G61"/>
+  <autoFilter ref="A4:G62"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"적용,검토중,미적용,해당없음"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/rag_project_log_rev1.xlsx
+++ b/docs/rag_project_log_rev1.xlsx
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_진행이력'!$A$4:$G$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_산출물목록'!$A$4:$G$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_산출물목록'!$A$4:$G$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3_파이프라인점검'!$A$4:$J$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4_골든셋현황'!$A$4:$J$204</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5_실험이력'!$A$4:$O$204</definedName>
@@ -3259,7 +3259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3978,17 +3978,17 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>문서</t>
+          <t>엑셀</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>rag_runbook_t2_rev1.html</t>
+          <t>rag_run_guide_rev1.xlsx</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>T2 보고서판 안내서 — 도식 13장 · 개념 설명용</t>
+          <t>실행 가이드 — 순서 · 통과 기준 · 설정 기입표</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>rag_runbook_rev1.html</t>
+          <t>rag_runbook_t2_rev1.html</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>실행 안내서(원본) — 절차 · FAQ 중심</t>
+          <t>T2 보고서판 안내서 — 도식 13장 · 개념 설명용</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -4025,7 +4025,11 @@
           <t>rag_lab/docs/</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="12" t="n"/>
     </row>
@@ -4037,12 +4041,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>rag_checklist_sheet_rev9.html</t>
+          <t>rag_runbook_rev1.html</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>단계별 체크리스트 · 소스별 컬럼 정의</t>
+          <t>실행 안내서(원본) — 절차 · FAQ 중심</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -4062,12 +4066,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>rag_design_guide_rev4.html</t>
+          <t>rag_checklist_sheet_rev9.html</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>설계 원본</t>
+          <t>단계별 체크리스트 · 소스별 컬럼 정의</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -4087,12 +4091,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>rag_quest_board_rev4.html</t>
+          <t>rag_design_guide_rev4.html</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>옵션 사전</t>
+          <t>설계 원본</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -4112,12 +4116,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>query_flow_example_rev2.html</t>
+          <t>rag_quest_board_rev4.html</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>혼합 질의 흐름 · 지표 정의서 예시</t>
+          <t>옵션 사전</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -4132,17 +4136,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>엑셀</t>
+          <t>문서</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>rag_project_log_rev1.xlsx</t>
+          <t>query_flow_example_rev2.html</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>이력 대장 — 본 파일</t>
+          <t>혼합 질의 흐름 · 지표 정의서 예시</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -4150,11 +4154,7 @@
           <t>rag_lab/docs/</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
+      <c r="E36" s="6" t="inlineStr"/>
       <c r="F36" s="12" t="n"/>
       <c r="G36" s="12" t="n"/>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>rag_checklist_rev10.xlsx</t>
+          <t>rag_project_log_rev1.xlsx</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>체크리스트 · 컬럼 정의 · 단계별 실행 도구(S번호↔노트북)</t>
+          <t>이력 대장 — 본 파일</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>신규 시트</t>
+          <t>신규</t>
         </is>
       </c>
       <c r="F37" s="12" t="n"/>
@@ -4195,12 +4195,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>golden_eval_pack_rev4.xlsx</t>
+          <t>rag_checklist_rev10.xlsx</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>골든셋 · 평가 기입본 (LLM 골든셋 검수 · 프리셋 열 포함)</t>
+          <t>체크리스트 · 컬럼 정의 · 단계별 실행 도구(S번호↔노트북)</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>신규 시트 1b</t>
+          <t>신규 시트</t>
         </is>
       </c>
       <c r="F38" s="12" t="n"/>
@@ -4224,12 +4224,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>golden_set_example_rev2.xlsx</t>
+          <t>golden_eval_pack_rev4.xlsx</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>골든셋 실물 예시 — LLM 생성 · 근거 연결 포함 9종</t>
+          <t>골든셋 · 평가 기입본 (LLM 골든셋 검수 · 프리셋 열 포함)</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>신규</t>
+          <t>신규 시트 1b</t>
         </is>
       </c>
       <c r="F39" s="12" t="n"/>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>metric_catalog_template_rev1.xlsx</t>
+          <t>golden_set_example_rev2.xlsx</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>정형 지표 정의서 양식</t>
+          <t>골든셋 실물 예시 — LLM 생성 · 근거 연결 포함 9종</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -4266,36 +4266,36 @@
           <t>rag_lab/docs/</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>데이터</t>
+          <t>엑셀</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>golden/answer_golden_v1.csv</t>
+          <t>metric_catalog_template_rev1.xlsx</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>사외 정보 기반 질문 60건</t>
+          <t>정형 지표 정의서 양식</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>rag_lab/golden/</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>근거 연결 필요</t>
-        </is>
-      </c>
+          <t>rag_lab/docs/</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr"/>
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="12" t="n"/>
     </row>
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>golden/smoke20.csv</t>
+          <t>golden/answer_golden_v1.csv</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>스모크 20문항</t>
+          <t>사외 정보 기반 질문 60건</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -4320,16 +4320,36 @@
           <t>rag_lab/golden/</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>근거 연결 필요</t>
+        </is>
+      </c>
       <c r="F42" s="12" t="n"/>
       <c r="G42" s="12" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>데이터</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>golden/smoke20.csv</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>스모크 20문항</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>rag_lab/golden/</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr"/>
       <c r="F43" s="12" t="n"/>
       <c r="G43" s="12" t="n"/>
     </row>
@@ -4504,14 +4524,23 @@
       <c r="F62" s="12" t="n"/>
       <c r="G62" s="12" t="n"/>
     </row>
+    <row r="63">
+      <c r="A63" s="6" t="n"/>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="12" t="n"/>
+      <c r="G63" s="12" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G62"/>
+  <autoFilter ref="A4:G63"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"적용,검토중,미적용,해당없음"</formula1>
     </dataValidation>
   </dataValidations>
